--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -10339,7 +10339,7 @@
         <v>77</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>78</v>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -350,13 +350,13 @@
     <t>home.teachers.title</t>
   </si>
   <si>
-    <t>指導老師團隊</t>
+    <t>【師資團隊】</t>
   </si>
   <si>
     <t>home.teachers.desc</t>
   </si>
   <si>
-    <t>承蒙隆波帕默尊者慈悲教導，由弟子助教老師團隊親臨授課。</t>
+    <t>隆波帕默尊者體系助教老師 親臨授課指導</t>
   </si>
   <si>
     <t>home.teachers.online_title</t>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -131,7 +131,7 @@
     <t>home.nav.faq</t>
   </si>
   <si>
-    <t>常見問題</t>
+    <t>報名須知</t>
   </si>
   <si>
     <t>home.nav.register</t>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -602,13 +602,13 @@
     <t>home.faq.q5.title</t>
   </si>
   <si>
-    <t>飲食有什麼安排？</t>
+    <t>飲食安排？</t>
   </si>
   <si>
     <t>home.faq.q5.answer</t>
   </si>
   <si>
-    <t>每日提供早、午二餐素食，過午不食。飲食以清淡為主，禁五辛、酒類。如有特殊飲食需求（過敏、無麩質等），請於食宿登記時註明。</t>
+    <t>每日提供早餐、午餐、下午茶點與晚餐，提供葷食與素食選擇。不提供飲料與酒類。如有葷素需求或其他飲食習慣，請於報名時填寫，以利安排。</t>
   </si>
   <si>
     <t>首頁 &gt; FAQ &gt; Q6</t>
@@ -11341,7 +11341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
         <v>189</v>
       </c>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -617,13 +617,13 @@
     <t>home.faq.q6.title</t>
   </si>
   <si>
-    <t>交通如何前往？</t>
+    <t>交通方式與接駁安排</t>
   </si>
   <si>
     <t>home.faq.q6.answer</t>
   </si>
   <si>
-    <t>可自行前往日月潭禪修場地，亦可選擇主辦單位之台中／台北接駁服務。詳細路線、接駁集合時間與費用於錄取後於學員專區提供。</t>
+    <t>可自行開車或搭乘大眾運輸前往日月潭禪修場地，或選擇主辦單位提供之台北／台中／桃園機場（供國外學員）專車接送服務。接駁路線、集合地點、時間及費用，將於錄取後於學員專區公布。</t>
   </si>
   <si>
     <t>首頁 &gt; FAQ &gt; Q7</t>
@@ -11381,7 +11381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
         <v>194</v>
       </c>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -578,7 +578,7 @@
     <t>home.faq.q3.answer</t>
   </si>
   <si>
-    <t>是的，禪修期間全程禁語（除與助教老師小參時間外），這是維持禪修品質的重要規範。</t>
+    <t>是的。為維持禪修品質，禪修期間採全程禁語。除必要事務外，請將覺知帶回自身，時時保持覺知。靜默，是為了讓心更清晰地看見。</t>
   </si>
   <si>
     <t>首頁 &gt; FAQ &gt; Q4</t>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -587,13 +587,13 @@
     <t>home.faq.q4.title</t>
   </si>
   <si>
-    <t>住宿安排是怎樣的？</t>
+    <t>住宿安排如何？</t>
   </si>
   <si>
     <t>home.faq.q4.answer</t>
   </si>
   <si>
-    <t>於日月潭湖畔會館，提供雙人房、多人房等多種房型，含床具、棉被、毛巾等基本備品。詳細房型與費用於錄取後通知，並由學員專區完成登記。</t>
+    <t>本次住宿地點為日月潭湖畔會館。提供四人房型，每房皆為單人床，並設有兩套衛浴，配備床具、棉被與毛巾等基本用品。一次性盥洗用品（牙刷、牙膏、洗衣精等）需自行準備，會館未提供亦無販售。另請自備水杯、衣架與戶外拖鞋。</t>
   </si>
   <si>
     <t>首頁 &gt; FAQ &gt; Q5</t>
@@ -11301,7 +11301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" ht="72" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
         <v>184</v>
       </c>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -653,7 +653,7 @@
     <t>home.faq.q8.answer</t>
   </si>
   <si>
-    <t>建議準備寬鬆舒適的禪修服、個人盥洗用品、保暖衣物等。詳細打包清單會於錄取後一併提供。</t>
+    <t>建議攜帶寬鬆舒適的衣物，請穿著長褲，避免短褲及裙裝，並準備個人盥洗用品、保暖衣物（冷氣房內使用）及傘具。另請自備水杯、衣架、戶外拖鞋及個人常用藥品。如有個人習慣用品，亦可自行攜帶。台灣電壓為 110V，請自備充電器；國外學員建議攜帶電源轉接器。</t>
   </si>
   <si>
     <t>首頁 &gt; Footer</t>
@@ -11461,7 +11461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" ht="90" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
         <v>204</v>
       </c>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -467,13 +467,13 @@
     <t>home.timeline.item4.title</t>
   </si>
   <si>
-    <t>禪修正式開始</t>
+    <t>報到、入住後</t>
   </si>
   <si>
     <t>home.timeline.item4.desc</t>
   </si>
   <si>
-    <t>報到、安單、開始為期五日四夜的四念處禪修。</t>
+    <t>展開為期五日四夜的四念處禪修</t>
   </si>
   <si>
     <t>首頁 &gt; FAQ</t>
@@ -632,13 +632,13 @@
     <t>home.faq.q7.title</t>
   </si>
   <si>
-    <t>費用大約多少？</t>
+    <t>禪修需要費用嗎？</t>
   </si>
   <si>
     <t>home.faq.q7.answer</t>
   </si>
   <si>
-    <t>禪修課程本身免費。食宿、場地及交通等費用依房型由參加者自理，具體金額會在錄取通知中載明，並由學員專區完成登記繳費。</t>
+    <t>禪修課程免費。學員需負擔食宿等相關費用</t>
   </si>
   <si>
     <t>首頁 &gt; FAQ &gt; Q8</t>
@@ -11436,7 +11436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
         <v>199</v>
       </c>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -803,7 +803,7 @@
     <t>register.step1.fee_value</t>
   </si>
   <si>
-    <t>課程免費，食宿、場地及交通等費用自理（NT$18,600）</t>
+    <t>課程免費，食宿、場地及交通等費用自理</t>
   </si>
   <si>
     <t>報名表 &gt; Step1 &gt; 唯一路</t>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -1040,7 +1040,7 @@
     <t>register.q2.label</t>
   </si>
   <si>
-    <t>2. 是否以正式學員身份參加過隆波帕默尊者體系的實體或線上課程？</t>
+    <t>2. 您是否以正式學員身份參加過隆波帕默尊者體系所舉辦的實體或線上課程？</t>
   </si>
   <si>
     <t>報名表 &gt; Q3-8</t>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4317" uniqueCount="1493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4323" uniqueCount="1495">
   <si>
     <t>表單文案 ｜ 委託人核對／修改文件</t>
   </si>
@@ -872,7 +872,7 @@
     <t>register.step2.location_value</t>
   </si>
   <si>
-    <t>南投・日月潭湖畔會館</t>
+    <t>南投日月潭湖畔會館</t>
   </si>
   <si>
     <t>register.step2.capacity_value</t>
@@ -1130,7 +1130,7 @@
     <t>register.q9.label</t>
   </si>
   <si>
-    <t>9. 是否完整觀看／聆聽過至少 3 屆泰國四念處之旅的錄影／錄音？</t>
+    <t>9. 您是否完整地觀看／聆聽過至少 3 屆泰國四念處之旅的錄影／錄音？</t>
   </si>
   <si>
     <t>報名表 &gt; Q10</t>
@@ -1139,7 +1139,7 @@
     <t>register.q10.label</t>
   </si>
   <si>
-    <t>10. 您是否透過 ZOOM 的方式，獲得阿姜巴山、阿姜納、阿姜松、阿姜妮或阿姜沃伊的一對一禪修指導？</t>
+    <t>10. 您是否透過ZOOM的方式，獲得阿姜巴山、阿姜納、阿姜松、阿姜妮或阿姜沃伊做一對一的禪修指導？</t>
   </si>
   <si>
     <t>報名表 &gt; Q11</t>
@@ -1148,7 +1148,7 @@
     <t>register.q11.label</t>
   </si>
   <si>
-    <t>11. 是否觀看／聆聽過隆波帕默尊者法談開示 30 篇以上？</t>
+    <t>11. 您是否觀看／聆聽過隆波帕默尊者法談開示 30 篇以上？</t>
   </si>
   <si>
     <t>報名表 &gt; Q12</t>
@@ -1238,7 +1238,7 @@
     <t>register.q14.label</t>
   </si>
   <si>
-    <t>14. 過去三個月內，您做固定式練習的頻率是？</t>
+    <t>14. 在過去的三個月內，您做固定式練習的頻率是：</t>
   </si>
   <si>
     <t>報名表 &gt; Q14 選項</t>
@@ -1247,13 +1247,13 @@
     <t>register.q14.options.every_day</t>
   </si>
   <si>
-    <t>每天至少 30 分鐘</t>
+    <t>每天做固定形式的練習至少 30 分鐘</t>
   </si>
   <si>
     <t>register.q14.options.almost_every_day</t>
   </si>
   <si>
-    <t>幾乎每天，偶有間斷</t>
+    <t>幾乎每天都做固定形式的練習至少 30 分鐘，偶有間斷（三個月間斷不多於5天）</t>
   </si>
   <si>
     <t>register.q14.options.commit_from_now</t>
@@ -1268,7 +1268,7 @@
     <t>register.q15.label</t>
   </si>
   <si>
-    <t>15. 食宿、場地及交通等費用需由學員自行負擔，並請於 6/15 前完成支付。是否可於期限內完成？</t>
+    <t>15. 實體禪修課程之食宿、場地及交通等費用需由學員自行負擔，並請於 6 月 15 日前完成匯款或刷卡支付。請問您是否可於期限內完成付款？</t>
   </si>
   <si>
     <t>報名表 &gt; Q15 選項</t>
@@ -1280,13 +1280,19 @@
     <t>是，我願意按時全額支付</t>
   </si>
   <si>
+    <t>register.q15.options.no</t>
+  </si>
+  <si>
+    <t>否，我不願意支付</t>
+  </si>
+  <si>
     <t>報名表 &gt; Q16</t>
   </si>
   <si>
     <t>register.q16.label</t>
   </si>
   <si>
-    <t>16. 您是否身體健康，能夠全程獨立參與？</t>
+    <t>16. 您是否身體健康，能夠全程獨立參與實體禪修課程？</t>
   </si>
   <si>
     <t>報名表 &gt; Q17</t>
@@ -1364,7 +1370,7 @@
     <t>register.q21.label</t>
   </si>
   <si>
-    <t>21. 您屬於？</t>
+    <t>21. 請問您屬於：</t>
   </si>
   <si>
     <t>報名表 &gt; Q21 選項</t>
@@ -5235,16 +5241,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -5255,16 +5261,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -5275,16 +5281,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -5295,16 +5301,16 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -5315,16 +5321,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -5335,16 +5341,16 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -5355,16 +5361,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -5375,16 +5381,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -5395,16 +5401,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>156</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -5415,36 +5421,36 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -5455,36 +5461,36 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>332</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -5495,16 +5501,16 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -5515,36 +5521,36 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>332</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -5555,16 +5561,16 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>1</v>
@@ -5575,16 +5581,16 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>1</v>
@@ -5595,56 +5601,56 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="22" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>332</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>1</v>
@@ -5655,16 +5661,16 @@
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>1</v>
@@ -5675,16 +5681,16 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>1</v>
@@ -5695,56 +5701,56 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>332</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>1</v>
@@ -5755,16 +5761,16 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>1</v>
@@ -5775,16 +5781,16 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>1</v>
@@ -5795,16 +5801,16 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>1</v>
@@ -6001,16 +6007,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -6021,16 +6027,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -6041,56 +6047,56 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -6101,16 +6107,16 @@
     </row>
     <row r="7" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -6121,16 +6127,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -6141,16 +6147,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -6161,16 +6167,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -6181,16 +6187,16 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -6201,16 +6207,16 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -6221,16 +6227,16 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -6241,16 +6247,16 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -6261,16 +6267,16 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -6281,16 +6287,16 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -6301,16 +6307,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -6321,16 +6327,16 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>1</v>
@@ -6341,16 +6347,16 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>1</v>
@@ -6361,16 +6367,16 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>1</v>
@@ -6381,16 +6387,16 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>1</v>
@@ -6401,16 +6407,16 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>1</v>
@@ -6421,16 +6427,16 @@
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>1</v>
@@ -6441,16 +6447,16 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>1</v>
@@ -6461,16 +6467,16 @@
     </row>
     <row r="25" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>1</v>
@@ -6481,16 +6487,16 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>1</v>
@@ -6501,16 +6507,16 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>1</v>
@@ -6521,16 +6527,16 @@
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>1</v>
@@ -6541,16 +6547,16 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>1</v>
@@ -6561,16 +6567,16 @@
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>1</v>
@@ -6581,36 +6587,36 @@
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>1</v>
@@ -6621,16 +6627,16 @@
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B33" s="13" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C33" s="14" t="s">
         <v>1235</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>1233</v>
-      </c>
       <c r="D33" s="12" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>1</v>
@@ -6641,16 +6647,16 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>1</v>
@@ -6661,16 +6667,16 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>1</v>
@@ -6681,16 +6687,16 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>1</v>
@@ -6701,16 +6707,16 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>1</v>
@@ -6721,16 +6727,16 @@
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>1</v>
@@ -6741,16 +6747,16 @@
     </row>
     <row r="39" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>1</v>
@@ -6761,16 +6767,16 @@
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>1</v>
@@ -6781,16 +6787,16 @@
     </row>
     <row r="41" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>1</v>
@@ -6801,16 +6807,16 @@
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>1</v>
@@ -6821,16 +6827,16 @@
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>1</v>
@@ -6841,16 +6847,16 @@
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>1</v>
@@ -6861,16 +6867,16 @@
     </row>
     <row r="45" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>1</v>
@@ -6881,16 +6887,16 @@
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>1</v>
@@ -6901,16 +6907,16 @@
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>1</v>
@@ -6921,16 +6927,16 @@
     </row>
     <row r="48" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>1</v>
@@ -6941,16 +6947,16 @@
     </row>
     <row r="49" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>1</v>
@@ -6961,16 +6967,16 @@
     </row>
     <row r="50" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>1</v>
@@ -6981,16 +6987,16 @@
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>1</v>
@@ -7001,16 +7007,16 @@
     </row>
     <row r="52" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>1</v>
@@ -7021,16 +7027,16 @@
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C53" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>1</v>
@@ -7041,16 +7047,16 @@
     </row>
     <row r="54" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>1</v>
@@ -7061,16 +7067,16 @@
     </row>
     <row r="55" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>1</v>
@@ -7081,16 +7087,16 @@
     </row>
     <row r="56" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>1</v>
@@ -7101,16 +7107,16 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>1</v>
@@ -7121,16 +7127,16 @@
     </row>
     <row r="58" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>1</v>
@@ -7141,16 +7147,16 @@
     </row>
     <row r="59" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>1</v>
@@ -7161,16 +7167,16 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>1</v>
@@ -7181,16 +7187,16 @@
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="C61" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>1</v>
@@ -7201,16 +7207,16 @@
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>1</v>
@@ -7221,16 +7227,16 @@
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>1</v>
@@ -7241,16 +7247,16 @@
     </row>
     <row r="64" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>1</v>
@@ -7261,16 +7267,16 @@
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="C65" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>1</v>
@@ -7281,16 +7287,16 @@
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>1</v>
@@ -7301,16 +7307,16 @@
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>1</v>
@@ -7507,16 +7513,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -7527,16 +7533,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -7547,36 +7553,36 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -7587,16 +7593,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -7607,16 +7613,16 @@
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -7627,16 +7633,16 @@
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -7647,16 +7653,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -7667,16 +7673,16 @@
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -7687,16 +7693,16 @@
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -7707,16 +7713,16 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -7727,16 +7733,16 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -7933,16 +7939,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -7953,16 +7959,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -7973,16 +7979,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -7993,36 +7999,36 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -8033,56 +8039,56 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -8093,56 +8099,56 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -8153,36 +8159,36 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -8193,16 +8199,16 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -8213,16 +8219,16 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -8233,22 +8239,22 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -8439,16 +8445,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -8459,16 +8465,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -8479,36 +8485,36 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -8519,16 +8525,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -8539,16 +8545,16 @@
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -8559,16 +8565,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -8579,16 +8585,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -8599,16 +8605,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -8619,16 +8625,16 @@
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -8639,16 +8645,16 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -8659,16 +8665,16 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -8679,16 +8685,16 @@
     </row>
     <row r="14" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -8699,16 +8705,16 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -8719,16 +8725,16 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -8739,16 +8745,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -8945,16 +8951,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -8965,16 +8971,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -8985,36 +8991,36 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -9025,16 +9031,16 @@
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -9045,16 +9051,16 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -9065,16 +9071,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -9085,16 +9091,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -9105,16 +9111,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -9125,16 +9131,16 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -9145,16 +9151,16 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -9351,16 +9357,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -9371,16 +9377,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -9391,36 +9397,36 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -9431,16 +9437,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -9451,16 +9457,16 @@
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -9471,16 +9477,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -9491,16 +9497,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -9511,16 +9517,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -9717,116 +9723,116 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>1490</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -11776,7 +11782,7 @@
   <sheetPr>
     <tabColor rgb="FF495534"/>
   </sheetPr>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -12947,7 +12953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>371</v>
       </c>
@@ -13247,7 +13253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>404</v>
       </c>
@@ -13287,7 +13293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>411</v>
       </c>
@@ -13329,16 +13335,16 @@
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="B78" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="C78" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D78" s="7" t="s">
         <v>418</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>419</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>1</v>
@@ -13349,16 +13355,16 @@
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B79" s="13" t="s">
         <v>420</v>
-      </c>
-      <c r="B79" s="13" t="s">
-        <v>421</v>
       </c>
       <c r="C79" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>1</v>
@@ -13369,16 +13375,16 @@
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="C80" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D80" s="7" t="s">
         <v>424</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>425</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>1</v>
@@ -13389,7 +13395,7 @@
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B81" s="13" t="s">
         <v>426</v>
@@ -13409,16 +13415,16 @@
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>428</v>
       </c>
       <c r="C82" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D82" s="7" t="s">
         <v>429</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>430</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>1</v>
@@ -13429,16 +13435,16 @@
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="C83" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="D83" s="12" t="s">
         <v>432</v>
-      </c>
-      <c r="C83" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>433</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>1</v>
@@ -13449,13 +13455,13 @@
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>434</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>435</v>
@@ -13469,87 +13475,87 @@
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="B85" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="C85" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D85" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="C85" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>438</v>
-      </c>
       <c r="E85" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>439</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C86" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B87" s="13" t="s">
         <v>443</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>444</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="B88" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="C88" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D88" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="C88" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>448</v>
-      </c>
       <c r="E88" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>1</v>
+        <v>441</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B89" s="13" t="s">
         <v>449</v>
@@ -13569,16 +13575,16 @@
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="B90" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="C90" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D90" s="7" t="s">
         <v>452</v>
-      </c>
-      <c r="C90" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>453</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>1</v>
@@ -13589,107 +13595,107 @@
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="B91" s="13" t="s">
         <v>454</v>
-      </c>
-      <c r="B91" s="13" t="s">
-        <v>455</v>
       </c>
       <c r="C91" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>439</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="B92" s="8" t="s">
         <v>457</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>458</v>
       </c>
       <c r="C92" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B93" s="13" t="s">
         <v>460</v>
-      </c>
-      <c r="B93" s="13" t="s">
-        <v>461</v>
       </c>
       <c r="C93" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F93" s="15" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C94" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="B95" s="13" t="s">
         <v>467</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="C95" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D95" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="C95" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>469</v>
-      </c>
       <c r="E95" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F95" s="15" t="s">
-        <v>1</v>
+        <v>441</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>470</v>
@@ -13709,7 +13715,7 @@
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B97" s="13" t="s">
         <v>472</v>
@@ -13729,7 +13735,7 @@
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>474</v>
@@ -13749,7 +13755,7 @@
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B99" s="13" t="s">
         <v>476</v>
@@ -13769,7 +13775,7 @@
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>478</v>
@@ -13789,7 +13795,7 @@
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B101" s="13" t="s">
         <v>480</v>
@@ -13809,7 +13815,7 @@
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B102" s="8" t="s">
         <v>482</v>
@@ -13829,7 +13835,7 @@
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B103" s="13" t="s">
         <v>484</v>
@@ -13849,7 +13855,7 @@
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>486</v>
@@ -13869,7 +13875,7 @@
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B105" s="13" t="s">
         <v>488</v>
@@ -13889,7 +13895,7 @@
     </row>
     <row r="106" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B106" s="8" t="s">
         <v>490</v>
@@ -13909,7 +13915,7 @@
     </row>
     <row r="107" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B107" s="13" t="s">
         <v>492</v>
@@ -13929,33 +13935,33 @@
     </row>
     <row r="108" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B108" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="C108" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D108" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="C108" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>496</v>
-      </c>
       <c r="E108" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>439</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B109" s="13" t="s">
         <v>497</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>332</v>
+        <v>153</v>
       </c>
       <c r="D109" s="12" t="s">
         <v>498</v>
@@ -13964,58 +13970,58 @@
         <v>1</v>
       </c>
       <c r="F109" s="15" t="s">
-        <v>1</v>
+        <v>441</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="B110" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="B110" s="8" t="s">
+      <c r="C110" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="D110" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="C110" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>501</v>
-      </c>
       <c r="E110" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>439</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="B111" s="13" t="s">
         <v>502</v>
-      </c>
-      <c r="B111" s="13" t="s">
-        <v>503</v>
       </c>
       <c r="C111" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D111" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F111" s="15" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="7" t="s">
         <v>504</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F111" s="15" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="112" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="7" t="s">
-        <v>502</v>
       </c>
       <c r="B112" s="8" t="s">
         <v>505</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>332</v>
+        <v>153</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>506</v>
@@ -14024,21 +14030,21 @@
         <v>1</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="113" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B113" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="B113" s="13" t="s">
+      <c r="C113" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="D113" s="12" t="s">
         <v>508</v>
-      </c>
-      <c r="C113" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="D113" s="12" t="s">
-        <v>509</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>1</v>
@@ -14049,7 +14055,7 @@
     </row>
     <row r="114" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B114" s="8" t="s">
         <v>510</v>
@@ -14069,16 +14075,16 @@
     </row>
     <row r="115" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="B115" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="B115" s="13" t="s">
+      <c r="C115" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="D115" s="12" t="s">
         <v>513</v>
-      </c>
-      <c r="C115" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>514</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>1</v>
@@ -14089,13 +14095,13 @@
     </row>
     <row r="116" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B116" s="8" t="s">
         <v>515</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>516</v>
@@ -14109,33 +14115,33 @@
     </row>
     <row r="117" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="B117" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="B117" s="13" t="s">
+      <c r="C117" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D117" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="C117" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="D117" s="12" t="s">
+      <c r="E117" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F117" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="7" t="s">
         <v>519</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F117" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="7" t="s">
-        <v>517</v>
       </c>
       <c r="B118" s="8" t="s">
         <v>520</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>521</v>
@@ -14147,9 +14153,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B119" s="13" t="s">
         <v>522</v>
@@ -14169,13 +14175,13 @@
     </row>
     <row r="120" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B120" s="8" t="s">
         <v>524</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>525</v>
@@ -14187,15 +14193,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B121" s="13" t="s">
         <v>526</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="D121" s="12" t="s">
         <v>527</v>
@@ -14207,9 +14213,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B122" s="8" t="s">
         <v>528</v>
@@ -14227,18 +14233,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="B123" s="13" t="s">
         <v>530</v>
       </c>
-      <c r="B123" s="13" t="s">
+      <c r="C123" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D123" s="12" t="s">
         <v>531</v>
-      </c>
-      <c r="C123" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>532</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>1</v>
@@ -14249,7 +14255,7 @@
     </row>
     <row r="124" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B124" s="8" t="s">
         <v>533</v>
@@ -14269,7 +14275,7 @@
     </row>
     <row r="125" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B125" s="13" t="s">
         <v>535</v>
@@ -14289,7 +14295,7 @@
     </row>
     <row r="126" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B126" s="8" t="s">
         <v>537</v>
@@ -14307,15 +14313,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B127" s="13" t="s">
         <v>539</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="D127" s="12" t="s">
         <v>540</v>
@@ -14327,18 +14333,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="B128" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="B128" s="8" t="s">
+      <c r="C128" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D128" s="7" t="s">
         <v>542</v>
-      </c>
-      <c r="C128" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>543</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>1</v>
@@ -14349,7 +14355,7 @@
     </row>
     <row r="129" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B129" s="13" t="s">
         <v>544</v>
@@ -14367,29 +14373,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="B130" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="B130" s="8" t="s">
+      <c r="C130" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D130" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="C130" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D130" s="7" t="s">
+      <c r="E130" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F130" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="12" t="s">
         <v>548</v>
-      </c>
-      <c r="E130" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F130" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="12" t="s">
-        <v>546</v>
       </c>
       <c r="B131" s="13" t="s">
         <v>549</v>
@@ -14407,69 +14413,69 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>1</v>
-      </c>
-      <c r="B133" t="s">
-        <v>1</v>
-      </c>
-      <c r="C133" t="s">
-        <v>1</v>
-      </c>
-      <c r="D133" t="s">
-        <v>1</v>
-      </c>
-      <c r="E133" t="s">
-        <v>1</v>
-      </c>
-      <c r="F133" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="16" t="s">
+    <row r="132" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F132" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>1</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1</v>
+      </c>
+      <c r="E134" t="s">
+        <v>1</v>
+      </c>
+      <c r="F134" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="B134" s="16"/>
-      <c r="C134" s="16"/>
-      <c r="D134" s="16"/>
-      <c r="E134" s="16"/>
-      <c r="F134" s="16"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="17" t="s">
+      <c r="B135" s="16"/>
+      <c r="C135" s="16"/>
+      <c r="D135" s="16"/>
+      <c r="E135" s="16"/>
+      <c r="F135" s="16"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="B135" s="17"/>
-      <c r="C135" s="17"/>
-      <c r="D135" s="17"/>
-      <c r="E135" s="17"/>
-      <c r="F135" s="17"/>
-    </row>
-    <row r="136" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="B136" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C136" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="D136" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E136" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="F136" s="18" t="s">
-        <v>1</v>
-      </c>
+      <c r="B136" s="17"/>
+      <c r="C136" s="17"/>
+      <c r="D136" s="17"/>
+      <c r="E136" s="17"/>
+      <c r="F136" s="17"/>
     </row>
     <row r="137" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="18" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B137" s="18" t="s">
         <v>1</v>
@@ -14489,7 +14495,7 @@
     </row>
     <row r="138" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B138" s="18" t="s">
         <v>1</v>
@@ -14509,7 +14515,7 @@
     </row>
     <row r="139" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B139" s="18" t="s">
         <v>1</v>
@@ -14529,7 +14535,7 @@
     </row>
     <row r="140" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B140" s="18" t="s">
         <v>1</v>
@@ -14547,10 +14553,30 @@
         <v>1</v>
       </c>
     </row>
+    <row r="141" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B141" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C141" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="D141" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E141" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="F141" s="18" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A134:F134"/>
     <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A136:F136"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -14595,16 +14621,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -14615,16 +14641,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -14635,16 +14661,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -14655,16 +14681,16 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -14675,16 +14701,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -14695,16 +14721,16 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -14715,16 +14741,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -14735,16 +14761,16 @@
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>332</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -14755,16 +14781,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -14775,16 +14801,16 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -14795,16 +14821,16 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -14815,16 +14841,16 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -14835,16 +14861,16 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -15041,16 +15067,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -15061,16 +15087,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -15081,16 +15107,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -15101,16 +15127,16 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -15121,16 +15147,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>588</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -15141,16 +15167,16 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -15161,16 +15187,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -15181,36 +15207,36 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -15221,16 +15247,16 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>83</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -15241,16 +15267,16 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -15261,16 +15287,16 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -15281,16 +15307,16 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -15301,16 +15327,16 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -15321,16 +15347,16 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -15341,16 +15367,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -15361,16 +15387,16 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>1</v>
@@ -15381,16 +15407,16 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>1</v>
@@ -15401,16 +15427,16 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>1</v>
@@ -15421,16 +15447,16 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>1</v>
@@ -15441,16 +15467,16 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>1</v>
@@ -15461,16 +15487,16 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>1</v>
@@ -15481,16 +15507,16 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>1</v>
@@ -15501,16 +15527,16 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>1</v>
@@ -15521,16 +15547,16 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>1</v>
@@ -15541,16 +15567,16 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>1</v>
@@ -15561,16 +15587,16 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>1</v>
@@ -15581,16 +15607,16 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>1</v>
@@ -15601,16 +15627,16 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>1</v>
@@ -15621,16 +15647,16 @@
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>1</v>
@@ -15641,16 +15667,16 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>1</v>
@@ -15661,16 +15687,16 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>1</v>
@@ -15681,16 +15707,16 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>1</v>
@@ -15701,16 +15727,16 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>83</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>1</v>
@@ -15721,16 +15747,16 @@
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>1</v>
@@ -15741,16 +15767,16 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>1</v>
@@ -15761,16 +15787,16 @@
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>1</v>
@@ -15781,16 +15807,16 @@
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>1</v>
@@ -15987,16 +16013,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -16007,16 +16033,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -16027,16 +16053,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -16047,16 +16073,16 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -16067,16 +16093,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>678</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -16087,16 +16113,16 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -16107,16 +16133,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -16127,16 +16153,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -16147,16 +16173,16 @@
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>688</v>
-      </c>
       <c r="D10" s="7" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -16167,16 +16193,16 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -16187,16 +16213,16 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -16207,16 +16233,16 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -16227,16 +16253,16 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -16247,16 +16273,16 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -16267,56 +16293,56 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>1</v>
@@ -16327,36 +16353,36 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>1</v>
@@ -16367,16 +16393,16 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>1</v>
@@ -16387,16 +16413,16 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>1</v>
@@ -16407,16 +16433,16 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>1</v>
@@ -16427,16 +16453,16 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>1</v>
@@ -16447,16 +16473,16 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>1</v>
@@ -16467,16 +16493,16 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>1</v>
@@ -16487,16 +16513,16 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>1</v>
@@ -16507,16 +16533,16 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>1</v>
@@ -16527,16 +16553,16 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>1</v>
@@ -16547,16 +16573,16 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>1</v>
@@ -16567,16 +16593,16 @@
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>1</v>
@@ -16587,16 +16613,16 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>1</v>
@@ -16607,16 +16633,16 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>1</v>
@@ -16627,16 +16653,16 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>1</v>
@@ -16647,16 +16673,16 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>1</v>
@@ -16667,16 +16693,16 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>1</v>
@@ -16687,16 +16713,16 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>1</v>
@@ -16707,16 +16733,16 @@
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>1</v>
@@ -16727,16 +16753,16 @@
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>1</v>
@@ -16747,16 +16773,16 @@
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>1</v>
@@ -16767,16 +16793,16 @@
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>1</v>
@@ -16787,16 +16813,16 @@
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>1</v>
@@ -16807,16 +16833,16 @@
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>1</v>
@@ -16827,36 +16853,36 @@
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>1</v>
@@ -16867,36 +16893,36 @@
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>1</v>
@@ -16907,96 +16933,96 @@
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C49" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D49" s="12" t="s">
+        <v>786</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="15" t="s">
         <v>784</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C51" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>1</v>
@@ -17007,16 +17033,16 @@
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C53" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>1</v>
@@ -17027,16 +17053,16 @@
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>1</v>
@@ -17047,16 +17073,16 @@
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C55" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>1</v>
@@ -17067,16 +17093,16 @@
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>1</v>
@@ -17087,16 +17113,16 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>1</v>
@@ -17107,16 +17133,16 @@
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>1</v>
@@ -17127,16 +17153,16 @@
     </row>
     <row r="59" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C59" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>1</v>
@@ -17147,16 +17173,16 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>1</v>
@@ -17167,16 +17193,16 @@
     </row>
     <row r="61" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C61" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>1</v>
@@ -17187,16 +17213,16 @@
     </row>
     <row r="62" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>1</v>
@@ -17207,16 +17233,16 @@
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>1</v>
@@ -17227,16 +17253,16 @@
     </row>
     <row r="64" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>1</v>
@@ -17247,16 +17273,16 @@
     </row>
     <row r="65" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C65" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>1</v>
@@ -17267,16 +17293,16 @@
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>1</v>
@@ -17287,16 +17313,16 @@
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>1</v>
@@ -17307,16 +17333,16 @@
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>1</v>
@@ -17327,16 +17353,16 @@
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C69" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>1</v>
@@ -17347,16 +17373,16 @@
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>1</v>
@@ -17367,16 +17393,16 @@
     </row>
     <row r="71" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C71" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>1</v>
@@ -17387,16 +17413,16 @@
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C72" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>1</v>
@@ -17407,16 +17433,16 @@
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C73" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>1</v>
@@ -17427,16 +17453,16 @@
     </row>
     <row r="74" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C74" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>1</v>
@@ -17447,16 +17473,16 @@
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>1</v>
@@ -17467,16 +17493,16 @@
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="C76" s="9" t="s">
         <v>844</v>
       </c>
-      <c r="B76" s="8" t="s">
-        <v>845</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>842</v>
-      </c>
       <c r="D76" s="7" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>1</v>
@@ -17487,16 +17513,16 @@
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C77" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>1</v>
@@ -17507,16 +17533,16 @@
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>1</v>
@@ -17527,16 +17553,16 @@
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>1</v>
@@ -17547,16 +17573,16 @@
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>1</v>
@@ -17753,16 +17779,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -17773,16 +17799,16 @@
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -17793,16 +17819,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -17813,16 +17839,16 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>83</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -17833,16 +17859,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>156</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -17853,16 +17879,16 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>83</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -17873,16 +17899,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>156</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -17893,16 +17919,16 @@
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -17913,16 +17939,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -17933,16 +17959,16 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -17953,16 +17979,16 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -17973,16 +17999,16 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>83</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -17993,16 +18019,16 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -18013,16 +18039,16 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -18033,16 +18059,16 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -18053,16 +18079,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -18259,16 +18285,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -18279,16 +18305,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -18299,16 +18325,16 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -18319,16 +18345,16 @@
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -18339,16 +18365,16 @@
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -18359,16 +18385,16 @@
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -18379,16 +18405,16 @@
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -18399,16 +18425,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -18419,16 +18445,16 @@
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -18439,16 +18465,16 @@
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -18459,16 +18485,16 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -18479,16 +18505,16 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -18499,16 +18525,16 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -18519,16 +18545,16 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -18539,16 +18565,16 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -18559,16 +18585,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -18579,16 +18605,16 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>1</v>
@@ -18599,16 +18625,16 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>1</v>
@@ -18619,16 +18645,16 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>1</v>
@@ -18639,16 +18665,16 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>1</v>
@@ -18659,16 +18685,16 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>1</v>
@@ -18679,16 +18705,16 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>1</v>
@@ -18699,16 +18725,16 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>1</v>
@@ -18719,16 +18745,16 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>1</v>
@@ -18739,16 +18765,16 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>1</v>
@@ -18759,16 +18785,16 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>1</v>
@@ -18779,36 +18805,36 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>1</v>
@@ -18819,16 +18845,16 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>1</v>
@@ -18839,16 +18865,16 @@
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>1</v>
@@ -18859,16 +18885,16 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>1</v>
@@ -18879,16 +18905,16 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>1</v>
@@ -18899,16 +18925,16 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>1</v>
@@ -18919,16 +18945,16 @@
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>1</v>
@@ -18939,16 +18965,16 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>1</v>
@@ -18959,16 +18985,16 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>1</v>
@@ -19165,16 +19191,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -19185,16 +19211,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -19205,16 +19231,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -19225,16 +19251,16 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -19245,16 +19271,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>994</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>992</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>990</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -19265,16 +19291,16 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -19285,16 +19311,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -19305,16 +19331,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -19325,16 +19351,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -19345,16 +19371,16 @@
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -19365,16 +19391,16 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -19385,36 +19411,36 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -19425,16 +19451,16 @@
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -19445,16 +19471,16 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -19465,16 +19491,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -19485,16 +19511,16 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>1</v>
@@ -19505,16 +19531,16 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>1</v>
@@ -19525,16 +19551,16 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>1</v>
@@ -19545,16 +19571,16 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>1</v>
@@ -19565,16 +19591,16 @@
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>1</v>
@@ -19585,16 +19611,16 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>1</v>
@@ -19605,16 +19631,16 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>1</v>
@@ -19625,16 +19651,16 @@
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>1</v>
@@ -19645,16 +19671,16 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>1</v>
@@ -19665,16 +19691,16 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>1</v>
@@ -19685,16 +19711,16 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>1</v>
@@ -19705,16 +19731,16 @@
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>1</v>
@@ -19725,16 +19751,16 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>1</v>
@@ -19745,16 +19771,16 @@
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>1</v>
@@ -19765,16 +19791,16 @@
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>1</v>
@@ -19785,16 +19811,16 @@
     </row>
     <row r="33" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>1</v>
@@ -19805,16 +19831,16 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>1</v>
@@ -19825,16 +19851,16 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>1</v>
@@ -19845,16 +19871,16 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>1</v>
@@ -19865,16 +19891,16 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>1</v>
@@ -19885,16 +19911,16 @@
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>1</v>
@@ -19905,16 +19931,16 @@
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>1</v>
@@ -19925,16 +19951,16 @@
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>1</v>
@@ -19945,16 +19971,16 @@
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>1</v>
@@ -19965,16 +19991,16 @@
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>1</v>

--- a/docs/客戶交付/表單文案.xlsx
+++ b/docs/客戶交付/表單文案.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4323" uniqueCount="1495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4359" uniqueCount="1508">
   <si>
     <t>表單文案 ｜ 委託人核對／修改文件</t>
   </si>
@@ -2102,7 +2102,7 @@
     <t>警示</t>
   </si>
   <si>
-    <t>請慎重考慮並如實填寫。由於飯店條款限制，學會已先代墊食宿等費用，若取消報名，所付費用恕不退款、轉讓。</t>
+    <t>請慎重考慮並如實填寫。由於飯店條款限制，學會已先代墊食宿等費用，若取消報名，所付費用恕不退款、轉讓。感謝您的諒解。請確認您能全然接受主辦單位在課程期間對課程及防疫措施的安排。</t>
   </si>
   <si>
     <t>lodging.step1.alert.2</t>
@@ -2111,6 +2111,33 @@
     <t>本表單送出後僅能再修改一次（共 2 次送出機會），請務必確認後再送出。</t>
   </si>
   <si>
+    <t>lodging.step1.alert.3</t>
+  </si>
+  <si>
+    <t>表單成功提交後，系統將自動發送確認通知至您的電子信箱，請注意查收（含垃圾郵件）。</t>
+  </si>
+  <si>
+    <t>食宿 &gt; 入住日期</t>
+  </si>
+  <si>
+    <t>lodging.checkin_date.0818</t>
+  </si>
+  <si>
+    <t>8/18 入住</t>
+  </si>
+  <si>
+    <t>lodging.checkin_date.0819</t>
+  </si>
+  <si>
+    <t>8/19 入住</t>
+  </si>
+  <si>
+    <t>lodging.checkin_date.0820</t>
+  </si>
+  <si>
+    <t>8/20 入住</t>
+  </si>
+  <si>
     <t>食宿 &gt; 入住說明</t>
   </si>
   <si>
@@ -2288,16 +2315,28 @@
     <t>食宿 &gt; 過午不食</t>
   </si>
   <si>
+    <t>lodging.noon.fasting_yes</t>
+  </si>
+  <si>
+    <t>是，過午不食</t>
+  </si>
+  <si>
+    <t>lodging.noon.fasting_no</t>
+  </si>
+  <si>
+    <t>否，不是過午不食</t>
+  </si>
+  <si>
     <t>lodging.noon.before_noon</t>
   </si>
   <si>
-    <t>需要 12 點前吃</t>
+    <t>需於中午12點前用餐</t>
   </si>
   <si>
     <t>lodging.noon.after_noon</t>
   </si>
   <si>
-    <t>可以 12 點後吃</t>
+    <t>可於中午12點後用餐</t>
   </si>
   <si>
     <t>食宿 &gt; 茶點</t>
@@ -5241,10 +5280,10 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1088</v>
+        <v>1101</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
@@ -5261,16 +5300,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1089</v>
+        <v>1102</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1090</v>
+        <v>1103</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -5281,16 +5320,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1091</v>
+        <v>1104</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -5301,16 +5340,16 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -5321,16 +5360,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1096</v>
+        <v>1109</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -5341,16 +5380,16 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1097</v>
+        <v>1110</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>997</v>
+        <v>1010</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -5361,16 +5400,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1098</v>
+        <v>1111</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1099</v>
+        <v>1112</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1100</v>
+        <v>1113</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -5381,16 +5420,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1098</v>
+        <v>1111</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1101</v>
+        <v>1114</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1102</v>
+        <v>1115</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -5401,16 +5440,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1103</v>
+        <v>1116</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1104</v>
+        <v>1117</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>156</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -5421,16 +5460,16 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1107</v>
+        <v>1120</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1108</v>
+        <v>1121</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -5441,16 +5480,16 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>431</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1110</v>
+        <v>1123</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -5461,16 +5500,16 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1111</v>
+        <v>1124</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1112</v>
+        <v>1125</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1113</v>
+        <v>1126</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -5481,16 +5520,16 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1111</v>
+        <v>1124</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1114</v>
+        <v>1127</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>332</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1115</v>
+        <v>1128</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -5501,16 +5540,16 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1111</v>
+        <v>1124</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>431</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1117</v>
+        <v>1130</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -5521,16 +5560,16 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1119</v>
+        <v>1132</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1120</v>
+        <v>1133</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -5541,16 +5580,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>332</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -5561,16 +5600,16 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1123</v>
+        <v>1136</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>431</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1124</v>
+        <v>1137</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>1</v>
@@ -5581,16 +5620,16 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>1125</v>
+        <v>1138</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1126</v>
+        <v>1139</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1127</v>
+        <v>1140</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>1</v>
@@ -5601,16 +5640,16 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>1</v>
@@ -5621,36 +5660,36 @@
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>1134</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="22" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1135</v>
+        <v>1148</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>332</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1136</v>
+        <v>1149</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>1</v>
@@ -5661,16 +5700,16 @@
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1137</v>
+        <v>1150</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>431</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1138</v>
+        <v>1151</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>1</v>
@@ -5681,16 +5720,16 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1139</v>
+        <v>1152</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1140</v>
+        <v>1153</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1141</v>
+        <v>1154</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>1</v>
@@ -5701,16 +5740,16 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>1142</v>
+        <v>1155</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1143</v>
+        <v>1156</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1144</v>
+        <v>1157</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>1</v>
@@ -5721,36 +5760,36 @@
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1146</v>
+        <v>1159</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>1147</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>332</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1149</v>
+        <v>1162</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>1</v>
@@ -5761,16 +5800,16 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1150</v>
+        <v>1163</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1151</v>
+        <v>1164</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1152</v>
+        <v>1165</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>1</v>
@@ -5781,16 +5820,16 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>1150</v>
+        <v>1163</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>1153</v>
+        <v>1166</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>1</v>
@@ -5801,16 +5840,16 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1150</v>
+        <v>1163</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1155</v>
+        <v>1168</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>1</v>
@@ -6007,16 +6046,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1157</v>
+        <v>1170</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1158</v>
+        <v>1171</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1160</v>
+        <v>1173</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -6027,16 +6066,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1161</v>
+        <v>1174</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1162</v>
+        <v>1175</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1163</v>
+        <v>1176</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -6047,56 +6086,56 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1165</v>
+        <v>1178</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1166</v>
+        <v>1179</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1168</v>
+        <v>1181</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>1170</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1171</v>
+        <v>1184</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -6107,16 +6146,16 @@
     </row>
     <row r="7" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1171</v>
+        <v>1184</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1175</v>
+        <v>1188</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1176</v>
+        <v>1189</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -6127,16 +6166,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1178</v>
+        <v>1191</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -6147,16 +6186,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1180</v>
+        <v>1193</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -6167,16 +6206,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1184</v>
+        <v>1197</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -6187,16 +6226,16 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1186</v>
+        <v>1199</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -6207,16 +6246,16 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1187</v>
+        <v>1200</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>690</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1188</v>
+        <v>1201</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -6227,16 +6266,16 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1190</v>
+        <v>1203</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1191</v>
+        <v>1204</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -6247,16 +6286,16 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1192</v>
+        <v>1205</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1193</v>
+        <v>1206</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -6267,16 +6306,16 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>690</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -6287,16 +6326,16 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1197</v>
+        <v>1210</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -6307,16 +6346,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -6327,16 +6366,16 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1202</v>
+        <v>1215</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>1</v>
@@ -6347,16 +6386,16 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1204</v>
+        <v>1217</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>1</v>
@@ -6367,16 +6406,16 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>1</v>
@@ -6387,16 +6426,16 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>1207</v>
+        <v>1220</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>1</v>
@@ -6407,16 +6446,16 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1207</v>
+        <v>1220</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>1</v>
@@ -6427,16 +6466,16 @@
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>1207</v>
+        <v>1220</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>690</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>1</v>
@@ -6447,16 +6486,16 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1216</v>
+        <v>1229</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>1</v>
@@ -6467,16 +6506,16 @@
     </row>
     <row r="25" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>1</v>
@@ -6487,16 +6526,16 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1220</v>
+        <v>1233</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>1</v>
@@ -6507,16 +6546,16 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1222</v>
+        <v>1235</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1223</v>
+        <v>1236</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>1</v>
@@ -6527,16 +6566,16 @@
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1224</v>
+        <v>1237</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1225</v>
+        <v>1238</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>1</v>
@@ -6547,16 +6586,16 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>1226</v>
+        <v>1239</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>1</v>
@@ -6567,16 +6606,16 @@
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>1</v>
@@ -6587,36 +6626,36 @@
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>1230</v>
+        <v>1243</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>690</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>1232</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1234</v>
+        <v>1247</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1236</v>
+        <v>1249</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>1</v>
@@ -6627,16 +6666,16 @@
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>1238</v>
+        <v>1251</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>1</v>
@@ -6647,16 +6686,16 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1240</v>
+        <v>1253</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1241</v>
+        <v>1254</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>1</v>
@@ -6667,16 +6706,16 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>1242</v>
+        <v>1255</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>1243</v>
+        <v>1256</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>1</v>
@@ -6687,16 +6726,16 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>1244</v>
+        <v>1257</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1245</v>
+        <v>1258</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>1</v>
@@ -6707,16 +6746,16 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>1246</v>
+        <v>1259</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1248</v>
+        <v>1261</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>1</v>
@@ -6727,16 +6766,16 @@
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1249</v>
+        <v>1262</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>1250</v>
+        <v>1263</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>1</v>
@@ -6747,16 +6786,16 @@
     </row>
     <row r="39" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>1252</v>
+        <v>1265</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>1253</v>
+        <v>1266</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>1254</v>
+        <v>1267</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>1</v>
@@ -6767,16 +6806,16 @@
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1255</v>
+        <v>1268</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>1256</v>
+        <v>1269</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1257</v>
+        <v>1270</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>1</v>
@@ -6787,16 +6826,16 @@
     </row>
     <row r="41" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>1259</v>
+        <v>1272</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>1260</v>
+        <v>1273</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>1</v>
@@ -6807,16 +6846,16 @@
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>1261</v>
+        <v>1274</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>1</v>
@@ -6827,16 +6866,16 @@
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>1263</v>
+        <v>1276</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>832</v>
+        <v>845</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>1</v>
@@ -6847,16 +6886,16 @@
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>1264</v>
+        <v>1277</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1265</v>
+        <v>1278</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>1</v>
@@ -6867,16 +6906,16 @@
     </row>
     <row r="45" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>1266</v>
+        <v>1279</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>1267</v>
+        <v>1280</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>1</v>
@@ -6887,16 +6926,16 @@
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>1268</v>
+        <v>1281</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1269</v>
+        <v>1282</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>1</v>
@@ -6907,16 +6946,16 @@
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>1270</v>
+        <v>1283</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>1271</v>
+        <v>1284</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>1</v>
@@ -6927,16 +6966,16 @@
     </row>
     <row r="48" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>1272</v>
+        <v>1285</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1273</v>
+        <v>1286</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>1</v>
@@ -6947,16 +6986,16 @@
     </row>
     <row r="49" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>1274</v>
+        <v>1287</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>1275</v>
+        <v>1288</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>1</v>
@@ -6967,16 +7006,16 @@
     </row>
     <row r="50" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>1276</v>
+        <v>1289</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1277</v>
+        <v>1290</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>1</v>
@@ -6987,16 +7026,16 @@
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>1278</v>
+        <v>1291</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>1</v>
@@ -7007,16 +7046,16 @@
     </row>
     <row r="52" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1280</v>
+        <v>1293</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>1281</v>
+        <v>1294</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1282</v>
+        <v>1295</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>1</v>
@@ -7027,16 +7066,16 @@
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>1284</v>
+        <v>1297</v>
       </c>
       <c r="C53" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>1285</v>
+        <v>1298</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>1</v>
@@ -7047,16 +7086,16 @@
     </row>
     <row r="54" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>1286</v>
+        <v>1299</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1287</v>
+        <v>1300</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>1</v>
@@ -7067,16 +7106,16 @@
     </row>
     <row r="55" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>1288</v>
+        <v>1301</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>1289</v>
+        <v>1302</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>1</v>
@@ -7087,16 +7126,16 @@
     </row>
     <row r="56" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1290</v>
+        <v>1303</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1291</v>
+        <v>1304</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>1</v>
@@ -7107,16 +7146,16 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>1293</v>
+        <v>1306</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>1</v>
@@ -7127,16 +7166,16 @@
     </row>
     <row r="58" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>1294</v>
+        <v>1307</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>1</v>
@@ -7147,16 +7186,16 @@
     </row>
     <row r="59" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>1296</v>
+        <v>1309</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>1297</v>
+        <v>1310</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>1</v>
@@ -7167,16 +7206,16 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>1298</v>
+        <v>1311</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>1299</v>
+        <v>1312</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1300</v>
+        <v>1313</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>1</v>
@@ -7187,16 +7226,16 @@
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>1301</v>
+        <v>1314</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>1302</v>
+        <v>1315</v>
       </c>
       <c r="C61" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>1303</v>
+        <v>1316</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>1</v>
@@ -7207,16 +7246,16 @@
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>1301</v>
+        <v>1314</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1304</v>
+        <v>1317</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1305</v>
+        <v>1318</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>1</v>
@@ -7227,16 +7266,16 @@
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>1306</v>
+        <v>1319</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>1308</v>
+        <v>1321</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>1</v>
@@ -7247,16 +7286,16 @@
     </row>
     <row r="64" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>1306</v>
+        <v>1319</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1309</v>
+        <v>1322</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1310</v>
+        <v>1323</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>1</v>
@@ -7267,10 +7306,10 @@
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>1306</v>
+        <v>1319</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>1311</v>
+        <v>1324</v>
       </c>
       <c r="C65" s="14" t="s">
         <v>77</v>
@@ -7287,16 +7326,16 @@
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>1312</v>
+        <v>1325</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1313</v>
+        <v>1326</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1314</v>
+        <v>1327</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>1</v>
@@ -7307,10 +7346,10 @@
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>1312</v>
+        <v>1325</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>1315</v>
+        <v>1328</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>41</v>
@@ -7513,16 +7552,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1316</v>
+        <v>1329</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1317</v>
+        <v>1330</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1318</v>
+        <v>1331</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -7533,16 +7572,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1319</v>
+        <v>1332</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1320</v>
+        <v>1333</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1321</v>
+        <v>1334</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -7553,36 +7592,36 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1323</v>
+        <v>1336</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1166</v>
+        <v>1179</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1324</v>
+        <v>1337</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1325</v>
+        <v>1338</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -7593,16 +7632,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1327</v>
+        <v>1340</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1328</v>
+        <v>1341</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -7613,16 +7652,16 @@
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1329</v>
+        <v>1342</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1330</v>
+        <v>1343</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -7633,16 +7672,16 @@
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1331</v>
+        <v>1344</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1332</v>
+        <v>1345</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -7653,16 +7692,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1333</v>
+        <v>1346</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -7673,16 +7712,16 @@
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1335</v>
+        <v>1348</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1336</v>
+        <v>1349</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -7693,16 +7732,16 @@
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1337</v>
+        <v>1350</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1338</v>
+        <v>1351</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -7713,16 +7752,16 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1339</v>
+        <v>1352</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1340</v>
+        <v>1353</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1341</v>
+        <v>1354</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -7733,16 +7772,16 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1342</v>
+        <v>1355</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1343</v>
+        <v>1356</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>690</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1344</v>
+        <v>1357</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -7939,16 +7978,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1345</v>
+        <v>1358</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1347</v>
+        <v>1360</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -7959,16 +7998,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1348</v>
+        <v>1361</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1349</v>
+        <v>1362</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1350</v>
+        <v>1363</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -7979,16 +8018,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1351</v>
+        <v>1364</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1352</v>
+        <v>1365</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1353</v>
+        <v>1366</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -7999,36 +8038,36 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1354</v>
+        <v>1367</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1355</v>
+        <v>1368</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1166</v>
+        <v>1179</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1354</v>
+        <v>1367</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1356</v>
+        <v>1369</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1357</v>
+        <v>1370</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -8039,56 +8078,56 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1359</v>
+        <v>1372</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1360</v>
+        <v>1373</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>1361</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1362</v>
+        <v>1375</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1363</v>
+        <v>1376</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>1364</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1366</v>
+        <v>1379</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -8099,56 +8138,56 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1368</v>
+        <v>1381</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1369</v>
+        <v>1382</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>1361</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1368</v>
+        <v>1381</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1371</v>
+        <v>1384</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1372</v>
+        <v>1385</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1374</v>
+        <v>1387</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -8159,36 +8198,36 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1377</v>
+        <v>1390</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1378</v>
+        <v>1391</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1379</v>
+        <v>1392</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>1380</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1377</v>
+        <v>1390</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1381</v>
+        <v>1394</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -8199,16 +8238,16 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1377</v>
+        <v>1390</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1383</v>
+        <v>1396</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1384</v>
+        <v>1397</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -8219,16 +8258,16 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1377</v>
+        <v>1390</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1385</v>
+        <v>1398</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1386</v>
+        <v>1399</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -8239,22 +8278,22 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1387</v>
+        <v>1400</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>690</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1389</v>
+        <v>1402</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>1390</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -8445,16 +8484,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1391</v>
+        <v>1404</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1392</v>
+        <v>1405</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1393</v>
+        <v>1406</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -8465,16 +8504,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1395</v>
+        <v>1408</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1396</v>
+        <v>1409</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -8485,36 +8524,36 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1397</v>
+        <v>1410</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1398</v>
+        <v>1411</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1166</v>
+        <v>1179</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1397</v>
+        <v>1410</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1399</v>
+        <v>1412</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1400</v>
+        <v>1413</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -8525,16 +8564,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1401</v>
+        <v>1414</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1402</v>
+        <v>1415</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1403</v>
+        <v>1416</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -8545,16 +8584,16 @@
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1401</v>
+        <v>1414</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1404</v>
+        <v>1417</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1405</v>
+        <v>1418</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -8565,16 +8604,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1406</v>
+        <v>1419</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1407</v>
+        <v>1420</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1408</v>
+        <v>1421</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -8585,16 +8624,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1406</v>
+        <v>1419</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1409</v>
+        <v>1422</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1410</v>
+        <v>1423</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -8605,16 +8644,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1411</v>
+        <v>1424</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1412</v>
+        <v>1425</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1413</v>
+        <v>1426</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -8625,16 +8664,16 @@
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1411</v>
+        <v>1424</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1414</v>
+        <v>1427</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1415</v>
+        <v>1428</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -8645,16 +8684,16 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1416</v>
+        <v>1429</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1417</v>
+        <v>1430</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1418</v>
+        <v>1431</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -8665,16 +8704,16 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1416</v>
+        <v>1429</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1419</v>
+        <v>1432</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1420</v>
+        <v>1433</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -8685,16 +8724,16 @@
     </row>
     <row r="14" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1416</v>
+        <v>1429</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1421</v>
+        <v>1434</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1422</v>
+        <v>1435</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -8705,16 +8744,16 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1416</v>
+        <v>1429</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1423</v>
+        <v>1436</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -8725,16 +8764,16 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1416</v>
+        <v>1429</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1425</v>
+        <v>1438</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1426</v>
+        <v>1439</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -8745,16 +8784,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1427</v>
+        <v>1440</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1428</v>
+        <v>1441</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1429</v>
+        <v>1442</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -8951,16 +8990,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1430</v>
+        <v>1443</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1431</v>
+        <v>1444</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1432</v>
+        <v>1445</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -8971,16 +9010,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1433</v>
+        <v>1446</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1434</v>
+        <v>1447</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1435</v>
+        <v>1448</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -8991,36 +9030,36 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1436</v>
+        <v>1449</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1437</v>
+        <v>1450</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1438</v>
+        <v>1451</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1436</v>
+        <v>1449</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1439</v>
+        <v>1452</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1440</v>
+        <v>1453</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -9031,16 +9070,16 @@
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1441</v>
+        <v>1454</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1442</v>
+        <v>1455</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>690</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1443</v>
+        <v>1456</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -9051,16 +9090,16 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1444</v>
+        <v>1457</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1445</v>
+        <v>1458</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1446</v>
+        <v>1459</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -9071,16 +9110,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1447</v>
+        <v>1460</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1448</v>
+        <v>1461</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1449</v>
+        <v>1462</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -9091,16 +9130,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1450</v>
+        <v>1463</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1451</v>
+        <v>1464</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -9111,16 +9150,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1450</v>
+        <v>1463</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1453</v>
+        <v>1466</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1454</v>
+        <v>1467</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -9131,16 +9170,16 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1450</v>
+        <v>1463</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1455</v>
+        <v>1468</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1456</v>
+        <v>1469</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -9151,16 +9190,16 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1450</v>
+        <v>1463</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1457</v>
+        <v>1470</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1204</v>
+        <v>1217</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -9357,16 +9396,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1458</v>
+        <v>1471</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1459</v>
+        <v>1472</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1460</v>
+        <v>1473</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -9377,16 +9416,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1461</v>
+        <v>1474</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1462</v>
+        <v>1475</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -9397,36 +9436,36 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1464</v>
+        <v>1477</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1465</v>
+        <v>1478</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1438</v>
+        <v>1451</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1464</v>
+        <v>1477</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1466</v>
+        <v>1479</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1467</v>
+        <v>1480</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -9437,16 +9476,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1468</v>
+        <v>1481</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1469</v>
+        <v>1482</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1470</v>
+        <v>1483</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -9457,16 +9496,16 @@
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1468</v>
+        <v>1481</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1471</v>
+        <v>1484</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1472</v>
+        <v>1485</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -9477,16 +9516,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1473</v>
+        <v>1486</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1474</v>
+        <v>1487</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1475</v>
+        <v>1488</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -9497,16 +9536,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1473</v>
+        <v>1486</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1476</v>
+        <v>1489</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1477</v>
+        <v>1490</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -9517,16 +9556,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1478</v>
+        <v>1491</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1479</v>
+        <v>1492</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1480</v>
+        <v>1493</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -9723,30 +9762,30 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1481</v>
+        <v>1494</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1482</v>
+        <v>1495</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1314</v>
+        <v>1327</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>1483</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1481</v>
+        <v>1494</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1484</v>
+        <v>1497</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>41</v>
@@ -9758,81 +9797,81 @@
         <v>1</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1483</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1486</v>
+        <v>1499</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1487</v>
+        <v>1500</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1483</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>1488</v>
+        <v>1501</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1489</v>
+        <v>1502</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1487</v>
+        <v>1500</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>1490</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1488</v>
+        <v>1501</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1491</v>
+        <v>1504</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1492</v>
+        <v>1505</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>1490</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1488</v>
+        <v>1501</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1493</v>
+        <v>1506</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1494</v>
+        <v>1507</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -15980,7 +16019,7 @@
   <sheetPr>
     <tabColor rgb="FF495534"/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -16151,7 +16190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>688</v>
       </c>
@@ -16191,35 +16230,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>694</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="C11" s="14" t="s">
+        <v>690</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>695</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="E11" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>696</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>694</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>697</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>698</v>
@@ -16233,13 +16272,13 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>699</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>700</v>
@@ -16253,13 +16292,13 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>701</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>702</v>
@@ -16273,16 +16312,16 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -16291,15 +16330,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>706</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>707</v>
@@ -16308,18 +16347,18 @@
         <v>1</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>441</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>708</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>709</v>
@@ -16328,18 +16367,18 @@
         <v>1</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>441</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>710</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>431</v>
+        <v>41</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>711</v>
@@ -16353,13 +16392,13 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>712</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>713</v>
@@ -16368,38 +16407,38 @@
         <v>1</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>441</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>431</v>
+        <v>153</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>1</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>717</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>327</v>
+        <v>153</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>718</v>
@@ -16408,18 +16447,18 @@
         <v>1</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>1</v>
+        <v>441</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>719</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>327</v>
+        <v>431</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>720</v>
@@ -16433,13 +16472,13 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>721</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>327</v>
+        <v>153</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>722</v>
@@ -16448,18 +16487,18 @@
         <v>1</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>1</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>723</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>327</v>
+        <v>431</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>724</v>
@@ -16473,16 +16512,16 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>1</v>
@@ -16493,13 +16532,13 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>728</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>729</v>
@@ -16513,13 +16552,13 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>730</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="D27" s="12" t="s">
         <v>731</v>
@@ -16533,13 +16572,13 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>732</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>733</v>
@@ -16553,13 +16592,13 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>734</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>735</v>
@@ -16579,7 +16618,7 @@
         <v>737</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>738</v>
@@ -16599,7 +16638,7 @@
         <v>739</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>327</v>
+        <v>41</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>740</v>
@@ -16619,7 +16658,7 @@
         <v>741</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>327</v>
+        <v>41</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>742</v>
@@ -16639,7 +16678,7 @@
         <v>743</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>327</v>
+        <v>41</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>744</v>
@@ -16653,16 +16692,16 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>1</v>
@@ -16673,7 +16712,7 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>748</v>
@@ -16693,7 +16732,7 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>750</v>
@@ -16713,16 +16752,16 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
+        <v>745</v>
+      </c>
+      <c r="B37" s="13" t="s">
         <v>752</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>753</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>1</v>
@@ -16733,16 +16772,16 @@
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>1</v>
@@ -16753,16 +16792,16 @@
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
+        <v>756</v>
+      </c>
+      <c r="B39" s="13" t="s">
         <v>757</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>758</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>1</v>
@@ -16773,16 +16812,16 @@
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>1</v>
@@ -16793,16 +16832,16 @@
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
+        <v>761</v>
+      </c>
+      <c r="B41" s="13" t="s">
         <v>762</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>763</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>1</v>
@@ -16813,36 +16852,36 @@
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D42" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>761</v>
+      </c>
+      <c r="B43" s="13" t="s">
         <v>766</v>
       </c>
-      <c r="E42" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
+      <c r="C43" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>767</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>768</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>769</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>1</v>
@@ -16853,36 +16892,36 @@
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>153</v>
+        <v>327</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>441</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>1</v>
@@ -16893,36 +16932,36 @@
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
+        <v>770</v>
+      </c>
+      <c r="B46" s="8" t="s">
         <v>773</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>776</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>778</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>1</v>
@@ -16933,116 +16972,116 @@
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>778</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>779</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="B49" s="13" t="s">
         <v>781</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="C49" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D49" s="12" t="s">
         <v>782</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>781</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>785</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>786</v>
-      </c>
       <c r="E49" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>784</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>789</v>
+        <v>441</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>153</v>
+        <v>327</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>792</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>1</v>
+        <v>791</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
+        <v>786</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>792</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>793</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>796</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>797</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>1</v>
@@ -17053,93 +17092,93 @@
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>1</v>
+        <v>797</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C55" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>1</v>
+        <v>797</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>1</v>
+        <v>802</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>1</v>
+        <v>805</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>807</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>808</v>
@@ -17151,18 +17190,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>809</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="C59" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>810</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>811</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>1</v>
@@ -17173,56 +17212,56 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>812</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="E60" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="B61" s="13" t="s">
         <v>813</v>
       </c>
-      <c r="C60" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D60" s="7" t="s">
+      <c r="C61" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D61" s="12" t="s">
         <v>814</v>
       </c>
-      <c r="E60" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
-        <v>812</v>
-      </c>
-      <c r="B61" s="13" t="s">
+      <c r="E61" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="C61" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D61" s="12" t="s">
+      <c r="C62" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>816</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>817</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>818</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>1</v>
@@ -17233,47 +17272,47 @@
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="B63" s="13" t="s">
+        <v>818</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D63" s="12" t="s">
         <v>819</v>
       </c>
-      <c r="C63" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D63" s="12" t="s">
+      <c r="E63" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>820</v>
       </c>
-      <c r="E63" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="B64" s="8" t="s">
+      <c r="C64" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D64" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="C64" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D64" s="7" t="s">
+      <c r="E64" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
         <v>822</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
-        <v>812</v>
       </c>
       <c r="B65" s="13" t="s">
         <v>823</v>
@@ -17293,16 +17332,16 @@
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>1</v>
@@ -17311,18 +17350,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>1</v>
@@ -17331,18 +17370,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>1</v>
@@ -17353,16 +17392,16 @@
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C69" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>1</v>
@@ -17371,18 +17410,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>1</v>
@@ -17393,16 +17432,16 @@
     </row>
     <row r="71" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C71" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>1</v>
@@ -17413,16 +17452,16 @@
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C72" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>1</v>
@@ -17433,16 +17472,16 @@
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C73" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>1</v>
@@ -17451,18 +17490,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C74" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>1</v>
@@ -17473,13 +17512,13 @@
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>844</v>
+        <v>41</v>
       </c>
       <c r="D75" s="12" t="s">
         <v>845</v>
@@ -17493,36 +17532,36 @@
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="B76" s="8" t="s">
         <v>846</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="C76" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D76" s="7" t="s">
         <v>847</v>
       </c>
-      <c r="C76" s="9" t="s">
-        <v>844</v>
-      </c>
-      <c r="D76" s="7" t="s">
+      <c r="E76" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="B77" s="13" t="s">
         <v>848</v>
       </c>
-      <c r="E76" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
+      <c r="C77" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>849</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>850</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>851</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>1</v>
@@ -17533,16 +17572,16 @@
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>849</v>
+        <v>825</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>1</v>
@@ -17553,188 +17592,308 @@
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>852</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>854</v>
-      </c>
-      <c r="B79" s="13" t="s">
-        <v>855</v>
-      </c>
-      <c r="C79" s="14" t="s">
-        <v>590</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>856</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F79" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
-        <v>854</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>857</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D80" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>856</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>857</v>
+      </c>
+      <c r="D81" s="12" t="s">
         <v>858</v>
       </c>
-      <c r="E80" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F80" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>1</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1</v>
-      </c>
-      <c r="C82" t="s">
-        <v>1</v>
-      </c>
-      <c r="D82" t="s">
-        <v>1</v>
-      </c>
-      <c r="E82" t="s">
-        <v>1</v>
-      </c>
-      <c r="F82" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="16" t="s">
+      <c r="E81" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
+        <v>859</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>863</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F83" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>868</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>590</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="7" t="s">
+        <v>867</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>871</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>1</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1</v>
+      </c>
+      <c r="E88" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="17" t="s">
+      <c r="B89" s="16"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="16"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="17"/>
-    </row>
-    <row r="85" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="18" t="s">
+      <c r="B90" s="17"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="17"/>
+      <c r="E90" s="17"/>
+      <c r="F90" s="17"/>
+    </row>
+    <row r="91" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="B85" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C85" s="18" t="s">
+      <c r="B91" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="D85" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" s="18" t="s">
+      <c r="D91" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E91" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="F85" s="18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="18" t="s">
+      <c r="F91" s="18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="B86" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C86" s="18" t="s">
+      <c r="B92" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C92" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="D86" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E86" s="18" t="s">
+      <c r="D92" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E92" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="F86" s="18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="18" t="s">
+      <c r="F92" s="18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="B87" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C87" s="18" t="s">
+      <c r="B93" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C93" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="D87" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E87" s="18" t="s">
+      <c r="D93" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E93" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="F87" s="18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="18" t="s">
+      <c r="F93" s="18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="B88" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C88" s="18" t="s">
+      <c r="B94" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C94" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="D88" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E88" s="18" t="s">
+      <c r="D94" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E94" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="F88" s="18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="18" t="s">
+      <c r="F94" s="18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="B89" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C89" s="18" t="s">
+      <c r="B95" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="D89" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E89" s="18" t="s">
+      <c r="D95" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E95" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="F89" s="18" t="s">
+      <c r="F95" s="18" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A90:F90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -17779,16 +17938,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>861</v>
+        <v>874</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -17799,16 +17958,16 @@
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>862</v>
+        <v>875</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -17819,16 +17978,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>864</v>
+        <v>877</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>865</v>
+        <v>878</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -17839,16 +17998,16 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>866</v>
+        <v>879</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>867</v>
+        <v>880</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>83</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>868</v>
+        <v>881</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -17859,16 +18018,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>866</v>
+        <v>879</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>869</v>
+        <v>882</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>156</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>870</v>
+        <v>883</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -17879,16 +18038,16 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>871</v>
+        <v>884</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>872</v>
+        <v>885</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>83</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>873</v>
+        <v>886</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -17899,16 +18058,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>871</v>
+        <v>884</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>874</v>
+        <v>887</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>156</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>875</v>
+        <v>888</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -17919,16 +18078,16 @@
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>876</v>
+        <v>889</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>877</v>
+        <v>890</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>878</v>
+        <v>891</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -17939,16 +18098,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>876</v>
+        <v>889</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>879</v>
+        <v>892</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>880</v>
+        <v>893</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -17959,16 +18118,16 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>876</v>
+        <v>889</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>881</v>
+        <v>894</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -17979,16 +18138,16 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>876</v>
+        <v>889</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>883</v>
+        <v>896</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>884</v>
+        <v>897</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -17999,16 +18158,16 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>885</v>
+        <v>898</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>886</v>
+        <v>899</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>83</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>887</v>
+        <v>900</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -18019,16 +18178,16 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>885</v>
+        <v>898</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>888</v>
+        <v>901</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -18039,16 +18198,16 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>890</v>
+        <v>903</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>891</v>
+        <v>904</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>892</v>
+        <v>905</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -18059,16 +18218,16 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>890</v>
+        <v>903</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>893</v>
+        <v>906</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>880</v>
+        <v>893</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -18079,16 +18238,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>890</v>
+        <v>903</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>894</v>
+        <v>907</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>895</v>
+        <v>908</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -18285,16 +18444,16 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>896</v>
+        <v>909</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>898</v>
+        <v>911</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>1</v>
@@ -18305,16 +18464,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>896</v>
+        <v>909</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>899</v>
+        <v>912</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>900</v>
+        <v>913</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -18325,16 +18484,16 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>896</v>
+        <v>909</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>901</v>
+        <v>914</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>902</v>
+        <v>915</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -18345,16 +18504,16 @@
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>904</v>
+        <v>917</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>905</v>
+        <v>918</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -18365,16 +18524,16 @@
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>907</v>
+        <v>920</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>908</v>
+        <v>921</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -18385,16 +18544,16 @@
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>909</v>
+        <v>922</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>910</v>
+        <v>923</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>911</v>
+        <v>924</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -18405,16 +18564,16 @@
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>912</v>
+        <v>925</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>913</v>
+        <v>926</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>914</v>
+        <v>927</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -18425,16 +18584,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>915</v>
+        <v>928</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>916</v>
+        <v>929</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>917</v>
+        <v>930</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -18445,16 +18604,16 @@
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>918</v>
+        <v>931</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>919</v>
+        <v>932</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>920</v>
+        <v>933</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -18465,16 +18624,16 @@
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>921</v>
+        <v>934</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>922</v>
+        <v>935</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>923</v>
+        <v>936</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -18485,16 +18644,16 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>924</v>
+        <v>937</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>925</v>
+        <v>938</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>926</v>
+        <v>939</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -18505,16 +18664,16 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>927</v>
+        <v>940</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>928</v>
+        <v>941</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>929</v>
+        <v>942</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
@@ -18525,16 +18684,16 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>927</v>
+        <v>940</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>930</v>
+        <v>943</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>690</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>931</v>
+        <v>944</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -18545,16 +18704,16 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>927</v>
+        <v>940</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>690</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -18565,16 +18724,16 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>927</v>
+        <v>940</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>934</v>
+        <v>947</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>690</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>935</v>
+        <v>948</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -18585,16 +18744,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>936</v>
+        <v>949</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>937</v>
+        <v>950</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>938</v>
+        <v>951</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -18605,16 +18764,16 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>936</v>
+        <v>949</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>939</v>
+        <v>952</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>940</v>
+        <v>953</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>1</v>
@@ -18625,16 +18784,16 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>941</v>
+        <v>954</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>942</v>
+        <v>955</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>590</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>943</v>
+        <v>956</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>1</v>
@@ -18645,16 +18804,16 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>941</v>
+        <v>954</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>944</v>
+        <v>957</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>1</v>
@@ -18665,16 +18824,16 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>941</v>
+        <v>954</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>946</v>
+        <v>959</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>590</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>947</v>
+        <v>960</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>1</v>
@@ -18685,16 +18844,16 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>949</v>
+        <v>962</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>950</v>
+        <v>963</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>1</v>
@@ -18705,16 +18864,16 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>951</v>
+        <v>964</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>952</v>
+        <v>965</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>1</v>
@@ -18725,16 +18884,16 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>953</v>
+        <v>966</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>954</v>
+        <v>967</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>1</v>
@@ -18745,16 +18904,16 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>955</v>
+        <v>968</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>956</v>
+        <v>969</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>1</v>
@@ -18765,16 +18924,16 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>957</v>
+        <v>970</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>958</v>
+        <v>971</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>1</v>
@@ -18785,16 +18944,16 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>959</v>
+        <v>972</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>960</v>
+        <v>973</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>1</v>
@@ -18805,36 +18964,36 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>961</v>
+        <v>974</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>690</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>962</v>
+        <v>975</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>963</v>
+        <v>976</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>964</v>
+        <v>977</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>690</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>965</v>
+        <v>978</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>1</v>
@@ -18845,16 +19004,16 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>966</v>
+        <v>979</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>967</v>
+        <v>980</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>968</v>
+        <v>981</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>1</v>
@@ -18865,16 +19024,16 @@
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>966</v>
+        <v>979</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>969</v>
+        <v>982</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>431</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>970</v>
+        <v>983</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>1</v>
@@ -18885,16 +19044,16 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>966</v>
+        <v>979</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>971</v>
+        <v>984</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>972</v>
+        <v>985</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>1</v>
@@ -18905,16 +19064,16 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>966</v>
+        <v>979</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>973</v>
+        <v>986</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>153</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>974</v>
+        <v>987</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>1</v>
@@ -18925,16 +19084,16 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>966</v>
+        <v>979</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>975</v>
+        <v>988</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>1</v>
@@ -18945,16 +19104,16 @@
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>977</v>
+        <v>990</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>978</v>
+        <v>991</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>979</v>
+        <v>992</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>1</v>
@@ -18965,16 +19124,16 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>977</v>
+        <v>990</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>980</v>
+        <v>993</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>981</v>
+        <v>994</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>1</v>
@@ -18985,16 +19144,16 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>977</v>
+        <v>990</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>982</v>
+        <v>995</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>983</v>
+        <v>996</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>1</v>
@@ -19191,10 +19350,10 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>984</v>
+        <v>997</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>985</v>
+        <v>998</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
@@ -19211,16 +19370,16 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>984</v>
+        <v>997</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>986</v>
+        <v>999</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>987</v>
+        <v>1000</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>1</v>
@@ -19231,16 +19390,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>984</v>
+        <v>997</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>988</v>
+        <v>1001</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>989</v>
+        <v>1002</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>1</v>
@@ -19251,16 +19410,16 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>991</v>
+        <v>1004</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>993</v>
+        <v>1006</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -19271,16 +19430,16 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>994</v>
+        <v>1007</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1</v>
@@ -19291,16 +19450,16 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>996</v>
+        <v>1009</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>997</v>
+        <v>1010</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -19311,16 +19470,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>998</v>
+        <v>1011</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>999</v>
+        <v>1012</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>1000</v>
+        <v>1013</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1001</v>
+        <v>1014</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -19331,16 +19490,16 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>998</v>
+        <v>1011</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1002</v>
+        <v>1015</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1003</v>
+        <v>1016</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -19351,16 +19510,16 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1004</v>
+        <v>1017</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1005</v>
+        <v>1018</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>1000</v>
+        <v>1013</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1006</v>
+        <v>1019</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>1</v>
@@ -19371,16 +19530,16 @@
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1004</v>
+        <v>1017</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1007</v>
+        <v>1020</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1008</v>
+        <v>1021</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>1</v>
@@ -19391,16 +19550,16 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1009</v>
+        <v>1022</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1010</v>
+        <v>1023</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>1000</v>
+        <v>1013</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1011</v>
+        <v>1024</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>1</v>
@@ -19411,36 +19570,36 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1009</v>
+        <v>1022</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1013</v>
+        <v>1026</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>1014</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1015</v>
+        <v>1028</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1016</v>
+        <v>1029</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1000</v>
+        <v>1013</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1017</v>
+        <v>1030</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>1</v>
@@ -19451,16 +19610,16 @@
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1015</v>
+        <v>1028</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1018</v>
+        <v>1031</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1019</v>
+        <v>1032</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>1</v>
@@ -19471,16 +19630,16 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1020</v>
+        <v>1033</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1021</v>
+        <v>1034</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>1</v>
@@ -19491,16 +19650,16 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1020</v>
+        <v>1033</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1022</v>
+        <v>1035</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1023</v>
+        <v>1036</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>1</v>
@@ -19511,16 +19670,16 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1020</v>
+        <v>1033</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1024</v>
+        <v>1037</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1025</v>
+        <v>1038</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>1</v>
@@ -19531,16 +19690,16 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>997</v>
+        <v>1010</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>1</v>
@@ -19551,16 +19710,16 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1029</v>
+        <v>1042</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>1</v>
@@ -19571,16 +19730,16 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1030</v>
+        <v>1043</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>1</v>
@@ -19591,16 +19750,16 @@
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1033</v>
+        <v>1046</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>1</v>
@@ -19611,16 +19770,16 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>1034</v>
+        <v>1047</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1035</v>
+        <v>1048</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1036</v>
+        <v>1049</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>1</v>
@@ -19631,16 +19790,16 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1034</v>
+        <v>1047</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>1</v>
@@ -19651,16 +19810,16 @@
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>1</v>
@@ -19671,16 +19830,16 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1042</v>
+        <v>1055</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1043</v>
+        <v>1056</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1044</v>
+        <v>1057</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>1</v>
@@ -19691,16 +19850,16 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>1</v>
@@ -19711,16 +19870,16 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1049</v>
+        <v>1062</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1050</v>
+        <v>1063</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>1</v>
@@ -19731,16 +19890,16 @@
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>1051</v>
+        <v>1064</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>1052</v>
+        <v>1065</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1053</v>
+        <v>1066</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>1</v>
@@ -19751,16 +19910,16 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1054</v>
+        <v>1067</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1055</v>
+        <v>1068</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1056</v>
+        <v>1069</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>1</v>
@@ -19771,16 +19930,16 @@
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>1057</v>
+        <v>1070</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>1058</v>
+        <v>1071</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>1</v>
@@ -19791,16 +19950,16 @@
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1061</v>
+        <v>1074</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1062</v>
+        <v>1075</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>1</v>
@@ -19811,16 +19970,16 @@
     </row>
     <row r="33" ht="54" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>1063</v>
+        <v>1076</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>1064</v>
+        <v>1077</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>1065</v>
+        <v>1078</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>1</v>
@@ -19831,16 +19990,16 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1067</v>
+        <v>1080</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1068</v>
+        <v>1081</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>1</v>
@@ -19851,16 +20010,16 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>1069</v>
+        <v>1082</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>1</v>
@@ -19871,16 +20030,16 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>1071</v>
+        <v>1084</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1072</v>
+        <v>1085</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>1</v>
@@ -19891,16 +20050,16 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>1073</v>
+        <v>1086</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1074</v>
+        <v>1087</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>1</v>
@@ -19911,16 +20070,16 @@
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1075</v>
+        <v>1088</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1077</v>
+        <v>1090</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>1</v>
@@ -19931,16 +20090,16 @@
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>1075</v>
+        <v>1088</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>1078</v>
+        <v>1091</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>1</v>
@@ -19951,16 +20110,16 @@
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1075</v>
+        <v>1088</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>1080</v>
+        <v>1093</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1081</v>
+        <v>1094</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>1</v>
@@ -19971,16 +20130,16 @@
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>1084</v>
+        <v>1097</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>1</v>
@@ -19991,16 +20150,16 @@
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>1</v>
